--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/服务内容表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/服务内容表.xlsx
@@ -464,7 +464,9 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>套</t>
@@ -475,7 +477,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -493,7 +499,9 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>套</t>
@@ -504,7 +512,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -522,7 +534,9 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>次</t>
@@ -533,7 +547,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -551,7 +569,9 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>套</t>
@@ -562,7 +582,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -580,7 +604,9 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>480</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>节点</t>
@@ -591,7 +617,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -609,7 +639,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>套</t>
@@ -620,7 +652,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -638,7 +674,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>套</t>
@@ -649,7 +687,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -667,7 +709,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>套</t>
@@ -678,7 +722,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -696,7 +744,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>套</t>
@@ -707,7 +757,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -725,7 +779,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>套</t>
@@ -736,7 +792,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -754,7 +814,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>套</t>
@@ -765,7 +827,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -783,7 +849,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>套</t>
@@ -794,7 +862,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -812,7 +884,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>套</t>
@@ -823,7 +897,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -841,7 +919,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>套</t>
@@ -852,7 +932,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -870,7 +954,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>套</t>
@@ -881,7 +967,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -899,7 +989,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>套</t>
@@ -910,7 +1002,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -928,7 +1024,9 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>次</t>
@@ -939,7 +1037,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -957,7 +1059,9 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>次</t>
@@ -968,7 +1072,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -986,7 +1094,9 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>套</t>
@@ -997,7 +1107,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1015,7 +1129,9 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>480</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1026,7 +1142,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1044,7 +1164,9 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>480</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1055,7 +1177,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1073,7 +1199,9 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>480</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1084,7 +1212,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1102,7 +1234,9 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>480</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1113,7 +1247,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -3132,9 +3270,7 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>10</v>
-      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>套</t>
@@ -3145,11 +3281,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3167,9 +3299,7 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>10</v>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>套</t>
@@ -3180,11 +3310,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3202,9 +3328,7 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>次</t>
@@ -3215,11 +3339,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3237,9 +3357,7 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>套</t>
@@ -3250,11 +3368,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3272,9 +3386,7 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>480</v>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3285,11 +3397,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3307,9 +3415,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>10</v>
-      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>套</t>
@@ -3320,11 +3426,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3342,9 +3444,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>10</v>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>套</t>
@@ -3355,11 +3455,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3377,9 +3473,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>10</v>
-      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>套</t>
@@ -3390,11 +3484,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3412,9 +3502,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>10</v>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>套</t>
@@ -3425,11 +3513,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3447,9 +3531,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>10</v>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>套</t>
@@ -3460,11 +3542,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3482,9 +3560,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>10</v>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>套</t>
@@ -3495,11 +3571,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3517,9 +3589,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>10</v>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>套</t>
@@ -3530,11 +3600,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3552,9 +3618,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>10</v>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>套</t>
@@ -3565,11 +3629,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3587,9 +3647,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>10</v>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>套</t>
@@ -3600,11 +3658,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3622,9 +3676,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>10</v>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>套</t>
@@ -3635,11 +3687,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3657,9 +3705,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>10</v>
-      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>套</t>
@@ -3670,11 +3716,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3692,9 +3734,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>次</t>
@@ -3705,11 +3745,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3727,9 +3763,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>次</t>
@@ -3740,11 +3774,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3762,9 +3792,7 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>1</v>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>套</t>
@@ -3775,11 +3803,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3797,9 +3821,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>480</v>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3810,11 +3832,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3832,9 +3850,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>480</v>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3845,11 +3861,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3867,9 +3879,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>480</v>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3880,11 +3890,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -3902,9 +3908,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>480</v>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3915,11 +3919,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
